--- a/results/result_evaluation_logs/C_Error_Incorporation_Gen1_PredEx.xlsx
+++ b/results/result_evaluation_logs/C_Error_Incorporation_Gen1_PredEx.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -625,11 +620,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>485b71ff-593d-462b-b710-05c2cf68c45a</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -704,11 +694,6 @@
 &lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/prop/direct/P2408&gt; &lt;http://www.wikidata.org/entity/Q120&gt; .
 &lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q17516&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4ab9c97d-2255-42ea-aa1b-cb5e0de96039</t>
         </is>
       </c>
     </row>
@@ -789,11 +774,6 @@
 &lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P108&gt; &lt;http://www.wikidata.org/entity/Q273626&gt; .
 &lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P184&gt; &lt;http://www.wikidata.org/entity/Q370496&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>87954363-a802-453b-921e-7cc524ddd402</t>
         </is>
       </c>
     </row>
@@ -878,11 +858,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>990fd5e4-4eec-4809-90c0-01197e21a7f3</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -956,11 +931,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q36771&gt; &lt;http://www.wikidata.org/entity/P569&gt; &lt;http://www.wikidata.org/entity/Q29999&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2fe8556a-ae5e-48f2-9847-e1f6a9808da8</t>
         </is>
       </c>
     </row>
@@ -1041,11 +1011,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>cb1945e2-3dcb-4d32-a01c-6766c0e0d110</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1120,11 +1085,6 @@
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/prop/direct/P31&gt; &lt;http://www.wikidata.org/entity/Q65943&gt; .
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/prop/direct/P138&gt; &lt;http://www.wikidata.org/entity/Q28937&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>cdb25703-b9c1-4dcf-bbfa-827de3c6d0f1</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1167,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>03e42793-4a9d-498c-9964-6c5696f42986</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1227,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1236,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1245,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1266,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1275,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1341,11 +1296,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>30f9604d-cf05-43a8-9bd5-7d304a28e9f9</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1422,11 +1372,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>ce7d0107-26c0-4b6e-b4db-0525693c8445</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1503,11 +1448,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>f014f8cf-4c2f-44f1-bdc0-7ba4b5344515</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1584,11 +1524,6 @@
 </t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>3f3dce62-7706-4555-90d9-0be904890bdd</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1663,11 +1598,6 @@
 &lt;http://www.wikidata.org/entity/Q7992209&gt; &lt;http://www.wikidata.org/entity/P4661&gt; &lt;http://www.wikidata.org/entity/Q3561541&gt; .
 &lt;http://www.wikidata.org/entity/Q3561541&gt; &lt;http://www.wikidata.org/entity/P200&gt; &lt;http://www.wikidata.org/entity/Q5364109&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>8e91a401-996e-491e-b5e3-99d13adf6f62</t>
         </is>
       </c>
     </row>
@@ -1750,11 +1680,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>be616b0a-c43f-41f2-8566-be706c9fff8c</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1828,11 +1753,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q3311362&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q66117&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>17e9c599-7935-4925-80dd-8b4fdb37a03f</t>
         </is>
       </c>
     </row>
@@ -1914,11 +1834,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9de5917f-e48d-4c11-b0c1-6dc4d765b01c</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1997,11 +1912,6 @@
 </t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>055216aa-e912-4927-bbf1-451779eeb1af</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2047,10 +1957,10 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
@@ -2084,11 +1994,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>fdb671d6-bdd8-4c55-a6e8-4062bbc10bc9</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2162,11 +2067,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q20671544&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/Q27914&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>adfa58a9-cc02-43e4-aab9-f840ec362f1d</t>
         </is>
       </c>
     </row>
@@ -2253,11 +2153,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9fc6edd9-c763-460c-9737-c6c0b5281856</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2336,11 +2231,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>defc0c1c-02c6-4c9a-a4b9-71311c55b294</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2415,11 +2305,6 @@
 &lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q430258&gt; .
 &lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P703&gt; &lt;http://www.wikidata.org/entity/Q15978631&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>7d416087-b4e6-4693-90f1-8f24facfb673</t>
         </is>
       </c>
     </row>
@@ -2514,11 +2399,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>edf387ab-e574-4a1f-b1f0-85188a5612ca</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2593,11 +2473,6 @@
 &lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/prop/direct/P86&gt; &lt;http://www.wikidata.org/entity/Q520445&gt; .
 &lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/prop/direct/P449&gt; &lt;http://www.wikidata.org/entity/Q220072&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>273de66a-2ddc-421c-aaf5-97f50f77b769</t>
         </is>
       </c>
     </row>
@@ -2681,11 +2556,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>b2106c7c-8bd3-4d46-bb7e-5632838782b5</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2762,11 +2632,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>590b2823-2909-4d58-bede-7b30046a7112</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2841,11 +2706,6 @@
 &lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .
 &lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>f0fdbe6e-8360-401f-96e4-120c60c93f41</t>
         </is>
       </c>
     </row>
@@ -2930,11 +2790,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>cd84e79b-44e4-483a-a412-dbce2b29acd5</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2950,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2959,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2968,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2989,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2998,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3064,11 +2919,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2a08266a-c1a7-477e-a005-5096d55d01d5</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3152,11 +3002,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>3a2b9988-39b4-434c-897e-9c370c745302</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3202,10 +3047,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
@@ -3233,11 +3078,6 @@
 &lt;http://www.wikidata.org/entity/Q65090308&gt; &lt;http://www.wikidata.org/entity/P674&gt; &lt;http://www.wikidata.org/entity/Q64876878&gt; .
 &lt;http://www.wikidata.org/entity/Q262170&gt; &lt;http://www.wikidata.org/entity/P725&gt; &lt;http://www.wikidata.org/entity/Q64876878&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>9558a45c-4992-491d-b45a-9f0c77500d3f</t>
         </is>
       </c>
     </row>
@@ -3320,11 +3160,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1a59195a-2ffd-40cb-aecf-502f1f9c5b17</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3400,11 +3235,6 @@
 &lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P2408&gt; &lt;http://www.wikidata.org/entity/Q2644&gt; .
 &lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q7843428&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>7b4c10d1-0ba2-4599-9881-ff527235708b</t>
         </is>
       </c>
     </row>
@@ -3489,11 +3319,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>237629fd-32e0-4784-99a1-50bbf454a94e</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3571,11 +3396,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>ed236706-bcc2-4aa8-a906-4776a272ba4f</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3591,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3600,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3609,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3630,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3639,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3705,11 +3525,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>19acc8c5-34a8-4ad0-8a2a-23628cb6be61</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3788,11 +3603,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>5d9d050c-2fa6-4567-a623-55cb11035771</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3867,11 +3677,6 @@
 &lt;http://www.wikidata.org/entity/Q907827&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .
 &lt;http://www.wikidata.org/entity/Q907827&gt; &lt;http://www.wikidata.org/entity/P1546&gt; &lt;http://www.wikidata.org/entity/Q877781&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>2598a73f-765c-4eaf-93c9-d72530e3a583</t>
         </is>
       </c>
     </row>
@@ -3951,11 +3756,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>78ce38f2-79c4-496b-a721-9a8c8272bde0</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4001,10 +3801,10 @@
         <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>3</v>
@@ -4034,11 +3834,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>f8b4ca59-c87d-481c-ab72-52226db316ea</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4084,10 +3879,10 @@
         <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
@@ -4120,11 +3915,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>856fb7e4-afce-4725-9d09-240a94165e27</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4199,11 +3989,6 @@
 &lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/prop/direct/P3373&gt; &lt;http://www.wikidata.org/entity/Q95994024&gt; .
 &lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>52adba54-192a-4ede-902a-83d6406f09c0</t>
         </is>
       </c>
     </row>
@@ -4283,11 +4068,6 @@
 </t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>2a05c7d1-45eb-4742-886b-c8bbe92d30a8</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4303,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4312,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4321,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4342,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4351,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4417,11 +4197,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>01a98c36-6d7b-462d-aa82-d2c7a1c276a1</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4499,11 +4274,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>98b95555-35d9-4b13-8f99-62a485970e7b</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4580,11 +4350,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>62d27be7-352e-41db-bcb6-290c214eb651</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4630,10 +4395,10 @@
         <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
         <v>3</v>
@@ -4669,11 +4434,6 @@
 </t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>2d26d77f-2267-4d7c-82c4-e9cbc2ebe145</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4689,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -4698,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -4707,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4728,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4737,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -4803,11 +4563,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>2fbefb89-941a-4f0b-8bcd-14b0082db863</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4887,11 +4642,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>a5dabd99-51fd-41f4-aa77-dec8fac160e4</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4965,11 +4715,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P556&gt; &lt;http://www.wikidata.org/entity/Q503601&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>697b4321-f2bf-4225-b8f8-5830cace709a</t>
         </is>
       </c>
     </row>
